--- a/sample_templates/期初存货.xlsx
+++ b/sample_templates/期初存货.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>物料号</t>
+          <t>物料编号</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -701,14 +701,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3. 必填列：物料号、结存数量、日期；其余列可留空，建议填写物料名称/分类名称/仓库名称/单位名称。</t>
+          <t>3. 必填列：物料编号、结存数量、日期；其余列可留空，建议填写物料名称/分类名称/仓库名称/单位名称。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4. 单价/金额可留空：系统按月末加权价自动计算（金额=结存数量×单价）。</t>
+          <t>4. 单价/金额可留空：系统按月末加权价自动回填（金额=结存数量×单价）。</t>
         </is>
       </c>
     </row>
